--- a/schedule/PDM_table_Week12.xlsx
+++ b/schedule/PDM_table_Week12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\DEGREE\SEM 2\AI PROJECT MANAGEMENT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFC09E1F-C013-4BA7-AB9C-25CFF56A5C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA1395C-5223-437E-ACB6-F83310A0A5C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C792D00B-F546-4EAC-94A7-EDF80D3D94D6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>Activity</t>
   </si>
@@ -82,6 +82,18 @@
   </si>
   <si>
     <t>H</t>
+  </si>
+  <si>
+    <t>Critical Path (PDM)</t>
+  </si>
+  <si>
+    <t>- Activities with zero slack: A, B, C, D, E, F, G, H</t>
+  </si>
+  <si>
+    <t>- Confirmed Critical Path: A → B → C → D → E → F → G → H</t>
+  </si>
+  <si>
+    <t>- Total Project Duration: 28 days</t>
   </si>
 </sst>
 </file>
@@ -453,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B40854C-41DD-4A52-B5F6-4254360E0225}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" customWidth="1"/>
@@ -668,6 +680,26 @@
         <v>28</v>
       </c>
     </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
